--- a/labeling_bbch_iso_dates.xlsx
+++ b/labeling_bbch_iso_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Ders\blg521\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C83F896-0337-4679-BF50-1FBD2050DEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD804091-6EBC-4AE3-A0E3-9FF15007FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="18588" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -150,6 +150,45 @@
   </si>
   <si>
     <t>BBCH 8</t>
+  </si>
+  <si>
+    <t>kullanılmadı</t>
+  </si>
+  <si>
+    <t>fotoğraf yoktu</t>
+  </si>
+  <si>
+    <t>foto sıkıntı</t>
+  </si>
+  <si>
+    <t>sıkıntı</t>
+  </si>
+  <si>
+    <t>14.01</t>
+  </si>
+  <si>
+    <t>hasat belli değil</t>
+  </si>
+  <si>
+    <t>17.01</t>
+  </si>
+  <si>
+    <t>17.02</t>
+  </si>
+  <si>
+    <t>2013 fotolar yok</t>
+  </si>
+  <si>
+    <t>18.04</t>
+  </si>
+  <si>
+    <t>21.05</t>
+  </si>
+  <si>
+    <t>01.17</t>
+  </si>
+  <si>
+    <t>21.06</t>
   </si>
 </sst>
 </file>
@@ -160,7 +199,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -219,8 +258,20 @@
       <sz val="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +307,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -308,7 +365,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -357,7 +414,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -391,6 +447,21 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -587,7 +658,7 @@
     <col min="23" max="23" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -654,39 +725,42 @@
       <c r="V1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="27">
+      <c r="W1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>34</v>
       </c>
       <c r="C2" s="10">
         <v>2014</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="24">
         <v>41978</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="25">
         <v>41989</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="25">
         <v>42012</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="25">
         <v>42065</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>42089</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <v>42106</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="27">
         <v>42141</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="28">
         <v>42165</v>
       </c>
       <c r="L2" s="5">
@@ -718,361 +792,362 @@
         <v>24</v>
       </c>
       <c r="S2" s="5">
-        <f t="shared" ref="S2:S19" si="4">SUM(L2:R2)</f>
+        <f t="shared" ref="S2:S26" si="4">SUM(L2:R2)</f>
         <v>187</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="29">
         <v>1</v>
       </c>
       <c r="U2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+    <row r="3" spans="1:23" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
         <v>2</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="10">
         <v>2016</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="25">
         <v>42690</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="25">
         <v>42726</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="25">
         <v>42752</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="25">
         <v>42800</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <v>42833</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="27">
         <v>42844</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="27">
         <v>42873</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <v>42894</v>
       </c>
       <c r="L3" s="5">
-        <f t="shared" ref="L3:L19" si="5">E3-D3</f>
+        <f t="shared" ref="L3:L26" si="5">E3-D3</f>
         <v>36</v>
       </c>
       <c r="M3" s="5">
-        <f t="shared" ref="M3:M19" si="6">F3-E3</f>
+        <f t="shared" ref="M3:M26" si="6">F3-E3</f>
         <v>26</v>
       </c>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N19" si="7">G3-F3</f>
+        <f t="shared" ref="N3:N26" si="7">G3-F3</f>
         <v>48</v>
       </c>
       <c r="O3" s="7">
-        <f t="shared" ref="O3:O19" si="8">H3-G3</f>
+        <f t="shared" ref="O3:O26" si="8">H3-G3</f>
         <v>33</v>
       </c>
       <c r="P3" s="5">
-        <f t="shared" ref="P3:P19" si="9">I3-H3</f>
+        <f t="shared" ref="P3:P26" si="9">I3-H3</f>
         <v>11</v>
       </c>
       <c r="Q3" s="5">
-        <f t="shared" ref="Q3:Q19" si="10">J3-I3</f>
+        <f t="shared" ref="Q3:Q26" si="10">J3-I3</f>
         <v>29</v>
       </c>
       <c r="R3" s="5">
-        <f t="shared" ref="R3:R19" si="11">K3-J3</f>
+        <f t="shared" ref="R3:R26" si="11">K3-J3</f>
         <v>21</v>
       </c>
       <c r="S3" s="5">
         <f t="shared" si="4"/>
         <v>204</v>
       </c>
-      <c r="T3" s="30">
+      <c r="T3" s="29">
         <v>2</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="W3" s="31">
+        <f>SUM(S2:S3)</f>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="26"/>
+      <c r="B4" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10">
+        <v>2016</v>
+      </c>
+      <c r="D4" s="25">
+        <v>42695</v>
+      </c>
+      <c r="E4" s="25">
+        <v>42717</v>
+      </c>
+      <c r="F4" s="25">
+        <v>42753</v>
+      </c>
+      <c r="G4" s="25">
+        <v>42782</v>
+      </c>
+      <c r="H4" s="27">
+        <v>42810</v>
+      </c>
+      <c r="I4" s="27">
+        <v>42821</v>
+      </c>
+      <c r="J4" s="27">
+        <v>42858</v>
+      </c>
+      <c r="K4" s="27">
+        <v>42885</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" ref="L4" si="12">E4-D4</f>
+        <v>22</v>
+      </c>
+      <c r="M4" s="5">
+        <f t="shared" ref="M4" si="13">F4-E4</f>
+        <v>36</v>
+      </c>
+      <c r="N4" s="5">
+        <f t="shared" ref="N4" si="14">G4-F4</f>
+        <v>29</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" ref="O4" si="15">H4-G4</f>
+        <v>28</v>
+      </c>
+      <c r="P4" s="5">
+        <f t="shared" ref="P4" si="16">I4-H4</f>
+        <v>11</v>
+      </c>
+      <c r="Q4" s="5">
+        <f t="shared" ref="Q4" si="17">J4-I4</f>
+        <v>37</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" ref="R4" si="18">K4-J4</f>
+        <v>27</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" ref="S4" si="19">SUM(L4:R4)</f>
+        <v>190</v>
+      </c>
+      <c r="T4" s="29">
+        <v>1</v>
+      </c>
+      <c r="U4" s="8"/>
+      <c r="W4" s="31"/>
+    </row>
+    <row r="5" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>2014</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D5" s="20">
         <v>41975</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E5" s="20">
         <v>41997</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F5" s="20">
         <v>42054</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G5" s="20">
         <v>42069</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H5" s="20">
         <v>42125</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I5" s="20">
         <v>42141</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J5" s="20">
         <v>42152</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K5" s="20">
         <v>42187</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L5" s="5">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M5" s="5">
         <f t="shared" si="6"/>
         <v>57</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N5" s="5">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O5" s="7">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P5" s="5">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q5" s="5">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R5" s="5">
         <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S5" s="5">
         <f t="shared" si="4"/>
         <v>212</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T5" s="8">
         <v>1</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+    <row r="6" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>2013</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D6" s="20">
         <v>41581</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E6" s="20">
         <v>41595</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F6" s="20">
         <v>41670</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G6" s="20">
         <v>41705</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H6" s="20">
         <v>41749</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I6" s="20">
         <v>41761</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J6" s="20">
         <v>41771</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K6" s="20">
         <v>41802</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L6" s="5">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M6" s="5">
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N6" s="5">
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O6" s="7">
         <f t="shared" si="8"/>
         <v>44</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P6" s="5">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q6" s="5">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R6" s="5">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S6" s="5">
         <f t="shared" si="4"/>
         <v>221</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T6" s="8">
         <v>1</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+    <row r="7" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C7" s="4">
         <v>2014</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D7" s="20">
         <v>41958</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E7" s="20">
         <v>41978</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F7" s="20">
         <v>42029</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G7" s="20">
         <v>42083</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H7" s="20">
         <v>42113</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I7" s="20">
         <v>42133</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J7" s="20">
         <v>42146</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K7" s="20">
         <v>42168</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L7" s="5">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M7" s="5">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N7" s="5">
         <f t="shared" si="7"/>
         <v>54</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O7" s="7">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P7" s="5">
         <f t="shared" si="9"/>
         <v>20</v>
-      </c>
-      <c r="Q6" s="5">
-        <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="R6" s="5">
-        <f t="shared" si="11"/>
-        <v>22</v>
-      </c>
-      <c r="S6" s="5">
-        <f t="shared" si="4"/>
-        <v>210</v>
-      </c>
-      <c r="T6" s="8">
-        <v>1</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2013</v>
-      </c>
-      <c r="D7" s="21">
-        <v>41602</v>
-      </c>
-      <c r="E7" s="21">
-        <v>41623</v>
-      </c>
-      <c r="F7" s="21">
-        <v>41685</v>
-      </c>
-      <c r="G7" s="21">
-        <v>41704</v>
-      </c>
-      <c r="H7" s="21">
-        <v>41749</v>
-      </c>
-      <c r="I7" s="21">
-        <v>41764</v>
-      </c>
-      <c r="J7" s="21">
-        <v>41777</v>
-      </c>
-      <c r="K7" s="21">
-        <v>41807</v>
-      </c>
-      <c r="L7" s="5">
-        <f t="shared" si="5"/>
-        <v>21</v>
-      </c>
-      <c r="M7" s="5">
-        <f t="shared" si="6"/>
-        <v>62</v>
-      </c>
-      <c r="N7" s="5">
-        <f t="shared" si="7"/>
-        <v>19</v>
-      </c>
-      <c r="O7" s="7">
-        <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="P7" s="5">
-        <f t="shared" si="9"/>
-        <v>15</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="10"/>
@@ -1080,11 +1155,11 @@
       </c>
       <c r="R7" s="5">
         <f t="shared" si="11"/>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="4"/>
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="T7" s="8">
         <v>1</v>
@@ -1093,51 +1168,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
-        <v>7</v>
+    <row r="8" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
         <v>2013</v>
       </c>
-      <c r="D8" s="21">
-        <v>41593</v>
-      </c>
-      <c r="E8" s="21">
-        <v>41633</v>
-      </c>
-      <c r="F8" s="21">
-        <v>41678</v>
-      </c>
-      <c r="G8" s="21">
+      <c r="D8" s="20">
+        <v>41602</v>
+      </c>
+      <c r="E8" s="20">
+        <v>41623</v>
+      </c>
+      <c r="F8" s="20">
+        <v>41685</v>
+      </c>
+      <c r="G8" s="20">
         <v>41704</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <v>41749</v>
       </c>
-      <c r="I8" s="21">
-        <v>41762</v>
-      </c>
-      <c r="J8" s="21">
-        <v>41779</v>
-      </c>
-      <c r="K8" s="21">
-        <v>41814</v>
+      <c r="I8" s="20">
+        <v>41764</v>
+      </c>
+      <c r="J8" s="20">
+        <v>41777</v>
+      </c>
+      <c r="K8" s="20">
+        <v>41807</v>
       </c>
       <c r="L8" s="5">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" si="8"/>
@@ -1145,19 +1220,19 @@
       </c>
       <c r="P8" s="5">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="11"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="4"/>
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="T8" s="8">
         <v>1</v>
@@ -1166,218 +1241,222 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <v>8</v>
+    <row r="9" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" ref="C9" si="12">YEAR(D9)</f>
-        <v>2016</v>
-      </c>
-      <c r="D9" s="21">
-        <v>42686</v>
-      </c>
-      <c r="E9" s="21">
-        <v>42711</v>
-      </c>
-      <c r="F9" s="21">
-        <v>42781</v>
-      </c>
-      <c r="G9" s="21">
-        <v>42810</v>
-      </c>
-      <c r="H9" s="21">
-        <v>42857</v>
-      </c>
-      <c r="I9" s="21">
-        <v>42871</v>
-      </c>
-      <c r="J9" s="21">
-        <v>42891</v>
-      </c>
-      <c r="K9" s="21">
-        <v>42906</v>
+        <v>2013</v>
+      </c>
+      <c r="D9" s="20">
+        <v>41593</v>
+      </c>
+      <c r="E9" s="20">
+        <v>41633</v>
+      </c>
+      <c r="F9" s="20">
+        <v>41678</v>
+      </c>
+      <c r="G9" s="20">
+        <v>41704</v>
+      </c>
+      <c r="H9" s="20">
+        <v>41749</v>
+      </c>
+      <c r="I9" s="20">
+        <v>41762</v>
+      </c>
+      <c r="J9" s="20">
+        <v>41779</v>
+      </c>
+      <c r="K9" s="20">
+        <v>41814</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" si="8"/>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="4"/>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T9" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
+    <row r="10" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4">
-        <v>2013</v>
-      </c>
-      <c r="D10" s="21">
-        <v>41592</v>
-      </c>
-      <c r="E10" s="21">
-        <v>41697</v>
-      </c>
-      <c r="F10" s="21">
-        <v>41727</v>
-      </c>
-      <c r="G10" s="21">
-        <v>41751</v>
-      </c>
-      <c r="H10" s="21">
-        <v>41781</v>
-      </c>
-      <c r="I10" s="21">
-        <v>41796</v>
-      </c>
-      <c r="J10" s="21">
-        <v>41815</v>
-      </c>
-      <c r="K10" s="21">
-        <v>41842</v>
+        <f t="shared" ref="C10" si="20">YEAR(D10)</f>
+        <v>2016</v>
+      </c>
+      <c r="D10" s="20">
+        <v>42686</v>
+      </c>
+      <c r="E10" s="20">
+        <v>42711</v>
+      </c>
+      <c r="F10" s="20">
+        <v>42781</v>
+      </c>
+      <c r="G10" s="20">
+        <v>42810</v>
+      </c>
+      <c r="H10" s="20">
+        <v>42857</v>
+      </c>
+      <c r="I10" s="20">
+        <v>42871</v>
+      </c>
+      <c r="J10" s="20">
+        <v>42891</v>
+      </c>
+      <c r="K10" s="20">
+        <v>42906</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="5"/>
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="11"/>
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="4"/>
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="T10" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
-        <v>10</v>
+      <c r="W10" s="31">
+        <f>SUM(S5:S10)</f>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="4">
         <v>2013</v>
       </c>
-      <c r="D11" s="21">
-        <v>41627</v>
-      </c>
-      <c r="E11" s="21">
-        <v>41683</v>
-      </c>
-      <c r="F11" s="21">
-        <v>41723</v>
-      </c>
-      <c r="G11" s="21">
+      <c r="D11" s="20">
+        <v>41592</v>
+      </c>
+      <c r="E11" s="20">
+        <v>41697</v>
+      </c>
+      <c r="F11" s="20">
+        <v>41727</v>
+      </c>
+      <c r="G11" s="20">
         <v>41751</v>
       </c>
-      <c r="H11" s="21">
-        <v>41782</v>
-      </c>
-      <c r="I11" s="21">
-        <v>41794</v>
-      </c>
-      <c r="J11" s="21">
-        <v>41824</v>
-      </c>
-      <c r="K11" s="21">
-        <v>41844</v>
+      <c r="H11" s="20">
+        <v>41781</v>
+      </c>
+      <c r="I11" s="20">
+        <v>41796</v>
+      </c>
+      <c r="J11" s="20">
+        <v>41815</v>
+      </c>
+      <c r="K11" s="20">
+        <v>41842</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="5"/>
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="M11" s="5">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" si="8"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="4"/>
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="T11" s="8">
         <v>1</v>
@@ -1386,71 +1465,71 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
-        <v>11</v>
+    <row r="12" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D12" s="21">
-        <v>42636</v>
-      </c>
-      <c r="E12" s="21">
-        <v>42799</v>
-      </c>
-      <c r="F12" s="21">
-        <v>42841</v>
-      </c>
-      <c r="G12" s="21">
-        <v>42850</v>
-      </c>
-      <c r="H12" s="21">
-        <v>42882</v>
-      </c>
-      <c r="I12" s="21">
-        <v>42892</v>
-      </c>
-      <c r="J12" s="21">
-        <v>42925</v>
-      </c>
-      <c r="K12" s="21">
-        <v>42940</v>
+        <v>2013</v>
+      </c>
+      <c r="D12" s="20">
+        <v>41627</v>
+      </c>
+      <c r="E12" s="20">
+        <v>41683</v>
+      </c>
+      <c r="F12" s="20">
+        <v>41723</v>
+      </c>
+      <c r="G12" s="20">
+        <v>41751</v>
+      </c>
+      <c r="H12" s="20">
+        <v>41782</v>
+      </c>
+      <c r="I12" s="20">
+        <v>41794</v>
+      </c>
+      <c r="J12" s="20">
+        <v>41824</v>
+      </c>
+      <c r="K12" s="20">
+        <v>41844</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="5"/>
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="M12" s="5">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" si="8"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P12" s="5">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="4"/>
-        <v>304</v>
+        <v>217</v>
       </c>
       <c r="T12" s="8">
         <v>1</v>
@@ -1459,66 +1538,66 @@
         <v>7</v>
       </c>
       <c r="V12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>11</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4">
         <v>2016</v>
       </c>
-      <c r="D13" s="21">
-        <v>42701</v>
-      </c>
-      <c r="E13" s="21">
-        <v>42767</v>
-      </c>
-      <c r="F13" s="21">
-        <v>42804</v>
-      </c>
-      <c r="G13" s="21">
-        <v>42826</v>
-      </c>
-      <c r="H13" s="21">
-        <v>42865</v>
-      </c>
-      <c r="I13" s="21">
-        <v>42886</v>
-      </c>
-      <c r="J13" s="21">
-        <v>42911</v>
-      </c>
-      <c r="K13" s="21">
-        <v>42926</v>
+      <c r="D13" s="20">
+        <v>42636</v>
+      </c>
+      <c r="E13" s="20">
+        <v>42799</v>
+      </c>
+      <c r="F13" s="20">
+        <v>42841</v>
+      </c>
+      <c r="G13" s="20">
+        <v>42850</v>
+      </c>
+      <c r="H13" s="20">
+        <v>42882</v>
+      </c>
+      <c r="I13" s="20">
+        <v>42892</v>
+      </c>
+      <c r="J13" s="20">
+        <v>42925</v>
+      </c>
+      <c r="K13" s="20">
+        <v>42940</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="M13" s="5">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" si="8"/>
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="P13" s="5">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="11"/>
@@ -1526,7 +1605,7 @@
       </c>
       <c r="S13" s="5">
         <f t="shared" si="4"/>
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="T13" s="8">
         <v>1</v>
@@ -1534,60 +1613,63 @@
       <c r="U13" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="15">
+      <c r="V13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4">
         <v>2016</v>
       </c>
-      <c r="D14" s="22">
-        <v>42662</v>
-      </c>
-      <c r="E14" s="22">
-        <v>42777</v>
-      </c>
-      <c r="F14" s="22">
-        <v>42827</v>
-      </c>
-      <c r="G14" s="22">
-        <v>42860</v>
-      </c>
-      <c r="H14" s="22">
-        <v>42877</v>
-      </c>
-      <c r="I14" s="22">
-        <v>42884</v>
-      </c>
-      <c r="J14" s="22">
-        <v>42909</v>
-      </c>
-      <c r="K14" s="22">
-        <v>42939</v>
+      <c r="D14" s="20">
+        <v>42701</v>
+      </c>
+      <c r="E14" s="20">
+        <v>42767</v>
+      </c>
+      <c r="F14" s="20">
+        <v>42804</v>
+      </c>
+      <c r="G14" s="20">
+        <v>42826</v>
+      </c>
+      <c r="H14" s="20">
+        <v>42865</v>
+      </c>
+      <c r="I14" s="20">
+        <v>42886</v>
+      </c>
+      <c r="J14" s="20">
+        <v>42911</v>
+      </c>
+      <c r="K14" s="20">
+        <v>42926</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="7"/>
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="10"/>
@@ -1595,11 +1677,11 @@
       </c>
       <c r="R14" s="5">
         <f t="shared" si="11"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="4"/>
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="T14" s="8">
         <v>1</v>
@@ -1607,406 +1689,912 @@
       <c r="U14" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
+      <c r="V14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="33"/>
+      <c r="B15" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="34">
+        <v>2016</v>
+      </c>
+      <c r="D15" s="35">
+        <v>42667</v>
+      </c>
+      <c r="E15" s="35">
+        <v>42693</v>
+      </c>
+      <c r="F15" s="35">
+        <v>42805</v>
+      </c>
+      <c r="G15" s="35">
+        <v>42826</v>
+      </c>
+      <c r="H15" s="35">
+        <v>42881</v>
+      </c>
+      <c r="I15" s="35">
+        <v>42892</v>
+      </c>
+      <c r="J15" s="35">
+        <v>42904</v>
+      </c>
+      <c r="K15" s="35">
+        <v>42931</v>
+      </c>
+      <c r="L15" s="36">
+        <f t="shared" ref="L15:N19" si="21">E15-D15</f>
+        <v>26</v>
+      </c>
+      <c r="M15" s="36">
+        <f t="shared" si="21"/>
+        <v>112</v>
+      </c>
+      <c r="N15" s="36">
+        <f t="shared" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="O15" s="37">
+        <f t="shared" si="8"/>
+        <v>55</v>
+      </c>
+      <c r="P15" s="36">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="Q15" s="36">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="R15" s="36">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="S15" s="36">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+      <c r="T15" s="38">
+        <v>1</v>
+      </c>
+      <c r="U15" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="V15" s="39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="34">
+        <v>2013</v>
+      </c>
+      <c r="D16" s="35">
+        <v>41581</v>
+      </c>
+      <c r="E16" s="35">
+        <v>41605</v>
+      </c>
+      <c r="F16" s="35">
+        <v>41663</v>
+      </c>
+      <c r="G16" s="35">
+        <v>41705</v>
+      </c>
+      <c r="H16" s="35">
+        <v>41761</v>
+      </c>
+      <c r="I16" s="35">
+        <v>41784</v>
+      </c>
+      <c r="J16" s="35">
+        <v>41797</v>
+      </c>
+      <c r="K16" s="35">
+        <v>41810</v>
+      </c>
+      <c r="L16" s="36">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="M16" s="36">
+        <f t="shared" si="21"/>
+        <v>58</v>
+      </c>
+      <c r="N16" s="36">
+        <f t="shared" si="21"/>
+        <v>42</v>
+      </c>
+      <c r="O16" s="37">
+        <f t="shared" si="8"/>
+        <v>56</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="Q16" s="36">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="R16" s="36">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="4"/>
+        <v>229</v>
+      </c>
+      <c r="T16" s="8">
+        <v>1</v>
+      </c>
+      <c r="U16" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="V16" s="39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A17" s="33"/>
+      <c r="B17" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="34">
+        <v>2014</v>
+      </c>
+      <c r="D17" s="35">
+        <v>41925</v>
+      </c>
+      <c r="E17" s="35">
+        <v>41997</v>
+      </c>
+      <c r="F17" s="35">
+        <v>42065</v>
+      </c>
+      <c r="G17" s="35">
+        <v>42083</v>
+      </c>
+      <c r="H17" s="35">
+        <v>42131</v>
+      </c>
+      <c r="I17" s="35">
+        <v>42144</v>
+      </c>
+      <c r="J17" s="35">
+        <v>42160</v>
+      </c>
+      <c r="K17" s="35">
+        <v>42199</v>
+      </c>
+      <c r="L17" s="36">
+        <f t="shared" si="21"/>
+        <v>72</v>
+      </c>
+      <c r="M17" s="36">
+        <f t="shared" si="21"/>
+        <v>68</v>
+      </c>
+      <c r="N17" s="36">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="O17" s="37">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="9"/>
+        <v>13</v>
+      </c>
+      <c r="Q17" s="36">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="R17" s="36">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="S17" s="36">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+      <c r="T17" s="8">
+        <v>1</v>
+      </c>
+      <c r="U17" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A18" s="33"/>
+      <c r="B18" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="34">
+        <v>2016</v>
+      </c>
+      <c r="D18" s="35">
+        <v>42665</v>
+      </c>
+      <c r="E18" s="35">
+        <v>42793</v>
+      </c>
+      <c r="F18" s="35">
+        <v>42818</v>
+      </c>
+      <c r="G18" s="35">
+        <v>42844</v>
+      </c>
+      <c r="H18" s="35">
+        <v>42892</v>
+      </c>
+      <c r="I18" s="35">
+        <v>42904</v>
+      </c>
+      <c r="J18" s="35">
+        <v>42930</v>
+      </c>
+      <c r="K18" s="35">
+        <v>42951</v>
+      </c>
+      <c r="L18" s="36">
+        <f t="shared" si="21"/>
+        <v>128</v>
+      </c>
+      <c r="M18" s="36">
+        <f t="shared" si="21"/>
+        <v>25</v>
+      </c>
+      <c r="N18" s="36">
+        <f t="shared" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="O18" s="37">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="P18" s="36">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
+      <c r="Q18" s="36">
+        <f t="shared" si="10"/>
+        <v>26</v>
+      </c>
+      <c r="R18" s="36">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="S18" s="36">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+      <c r="T18" s="8">
+        <v>1</v>
+      </c>
+      <c r="U18" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A19" s="33"/>
+      <c r="B19" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="34">
+        <v>2013</v>
+      </c>
+      <c r="D19" s="35">
+        <v>41598</v>
+      </c>
+      <c r="E19" s="35">
+        <v>41612</v>
+      </c>
+      <c r="F19" s="35">
+        <v>41689</v>
+      </c>
+      <c r="G19" s="35">
+        <v>41705</v>
+      </c>
+      <c r="H19" s="35">
+        <v>41757</v>
+      </c>
+      <c r="I19" s="35">
+        <v>41774</v>
+      </c>
+      <c r="J19" s="35">
+        <v>41787</v>
+      </c>
+      <c r="K19" s="35">
+        <v>41808</v>
+      </c>
+      <c r="L19" s="36">
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="M19" s="36">
+        <f t="shared" si="21"/>
+        <v>77</v>
+      </c>
+      <c r="N19" s="36">
+        <f t="shared" si="21"/>
         <v>16</v>
       </c>
-      <c r="C15" s="15">
+      <c r="O19" s="37">
+        <f t="shared" si="8"/>
+        <v>52</v>
+      </c>
+      <c r="P19" s="36">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="Q19" s="36">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="R19" s="36">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="S19" s="36">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="T19" s="8">
+        <v>1</v>
+      </c>
+      <c r="U19" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" s="39" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
+      <c r="B20" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="38"/>
+    </row>
+    <row r="21" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="26">
+        <v>13</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="15">
         <v>2016</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D21" s="21">
+        <v>42662</v>
+      </c>
+      <c r="E21" s="21">
+        <v>42777</v>
+      </c>
+      <c r="F21" s="21">
+        <v>42827</v>
+      </c>
+      <c r="G21" s="21">
+        <v>42860</v>
+      </c>
+      <c r="H21" s="21">
+        <v>42877</v>
+      </c>
+      <c r="I21" s="21">
+        <v>42884</v>
+      </c>
+      <c r="J21" s="21">
+        <v>42909</v>
+      </c>
+      <c r="K21" s="21">
+        <v>42939</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="5"/>
+        <v>115</v>
+      </c>
+      <c r="M21" s="5">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" si="7"/>
+        <v>33</v>
+      </c>
+      <c r="O21" s="7">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+      <c r="P21" s="5">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="Q21" s="5">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="R21" s="5">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="4"/>
+        <v>277</v>
+      </c>
+      <c r="T21" s="8">
+        <v>1</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="26">
+        <v>14</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="15">
+        <v>2016</v>
+      </c>
+      <c r="D22" s="21">
         <v>42642</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E22" s="21">
         <v>42771</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F22" s="21">
         <v>42826</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G22" s="21">
         <v>42856</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H22" s="21">
         <v>42878</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I22" s="21">
         <v>42889</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J22" s="21">
         <v>42918</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K22" s="21">
         <v>42937</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L22" s="5">
         <f t="shared" si="5"/>
         <v>129</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M22" s="5">
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N22" s="5">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O22" s="7">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P22" s="5">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="Q22" s="5">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="R15" s="5">
+      <c r="R22" s="5">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="S15" s="5">
+      <c r="S22" s="5">
         <f t="shared" si="4"/>
         <v>295</v>
       </c>
-      <c r="T15" s="8">
+      <c r="T22" s="8">
         <v>1</v>
       </c>
-      <c r="U15" s="8" t="s">
+      <c r="U22" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="V22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B23" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C23" s="15">
         <v>2016</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D23" s="21">
         <v>42688</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E23" s="21">
         <v>42707</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F23" s="21">
         <v>42773</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G23" s="21">
         <v>42807</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H23" s="21">
         <v>42858</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I23" s="21">
         <v>42872</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J23" s="21">
         <v>42890</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K23" s="21">
         <v>42908</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L23" s="5">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M23" s="5">
         <f t="shared" si="6"/>
         <v>66</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N23" s="5">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O23" s="7">
         <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P23" s="5">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q23" s="5">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
-      <c r="R16" s="5">
+      <c r="R23" s="5">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="S16" s="5">
+      <c r="S23" s="5">
         <f t="shared" si="4"/>
         <v>220</v>
       </c>
-      <c r="T16" s="8">
+      <c r="T23" s="8">
         <v>1</v>
       </c>
-      <c r="U16" s="8" t="s">
+      <c r="U23" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
+      <c r="W23" s="31">
+        <f>SUM(S23:S25)</f>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C24" s="15">
         <v>2016</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D24" s="21">
         <v>42688</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E24" s="21">
         <v>42719</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F24" s="21">
         <v>42786</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G24" s="21">
         <v>42811</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H24" s="21">
         <v>42852</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I24" s="21">
         <v>42875</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J24" s="21">
         <v>42891</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K24" s="21">
         <v>42906</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L24" s="5">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M24" s="5">
         <f t="shared" si="6"/>
         <v>67</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N24" s="5">
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O24" s="7">
         <f t="shared" si="8"/>
         <v>41</v>
       </c>
-      <c r="P17" s="5">
+      <c r="P24" s="5">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="Q24" s="5">
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
-      <c r="R17" s="5">
+      <c r="R24" s="5">
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S24" s="5">
         <f t="shared" si="4"/>
         <v>218</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T24" s="8">
         <v>1</v>
       </c>
-      <c r="U17" s="8" t="s">
+      <c r="U24" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
+    <row r="25" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
         <v>17</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C25" s="15">
         <v>2013</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D25" s="21">
         <v>41610</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E25" s="21">
         <v>41634</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F25" s="21">
         <v>41668</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G25" s="21">
         <v>41709</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H25" s="21">
         <v>41745</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I25" s="21">
         <v>41764</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J25" s="21">
         <v>41793</v>
       </c>
-      <c r="K18" s="22">
+      <c r="K25" s="21">
         <v>41802</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L25" s="5">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M25" s="5">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N25" s="5">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O25" s="7">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P25" s="5">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q25" s="5">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R25" s="5">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="S18" s="5">
+      <c r="S25" s="5">
         <f t="shared" si="4"/>
         <v>192</v>
       </c>
-      <c r="T18" s="8">
+      <c r="T25" s="8">
         <v>1</v>
       </c>
-      <c r="U18" s="8" t="s">
+      <c r="U25" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C26" s="17">
         <v>2016</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D26" s="22">
         <v>42703</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E26" s="22">
         <v>42730</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F26" s="22">
         <v>42783</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G26" s="22">
         <v>42814</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H26" s="22">
         <v>42853</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I26" s="22">
         <v>42872</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J26" s="22">
         <v>42887</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K26" s="23">
         <v>42898</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L26" s="5">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M26" s="5">
         <f t="shared" si="6"/>
         <v>53</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N26" s="5">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O26" s="7">
         <f t="shared" si="8"/>
         <v>39</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P26" s="5">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q19" s="5">
+      <c r="Q26" s="5">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="R19" s="5">
+      <c r="R26" s="5">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="S19" s="5">
+      <c r="S26" s="5">
         <f t="shared" si="4"/>
         <v>195</v>
       </c>
-      <c r="T19" s="8">
+      <c r="T26" s="8">
         <v>1</v>
       </c>
-      <c r="U19" s="8" t="s">
+      <c r="U26" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="K20" s="19"/>
-      <c r="M20" s="20"/>
-    </row>
-    <row r="21" spans="1:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K27" s="19"/>
+      <c r="L27" s="31">
+        <f t="shared" ref="L27:S27" si="22">SUM(L2:L11)+L21+SUM(L23:L25)</f>
+        <v>505</v>
+      </c>
+      <c r="M27" s="31">
+        <f t="shared" si="22"/>
+        <v>692</v>
+      </c>
+      <c r="N27" s="31">
+        <f t="shared" si="22"/>
+        <v>465</v>
+      </c>
+      <c r="O27" s="31">
+        <f t="shared" si="22"/>
+        <v>527</v>
+      </c>
+      <c r="P27" s="31">
+        <f t="shared" si="22"/>
+        <v>207</v>
+      </c>
+      <c r="Q27" s="31">
+        <f t="shared" si="22"/>
+        <v>292</v>
+      </c>
+      <c r="R27" s="31">
+        <f t="shared" si="22"/>
+        <v>339</v>
+      </c>
+      <c r="S27" s="31">
+        <f t="shared" si="22"/>
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B4" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>